--- a/public/downloads/AraComputational2022.xlsx
+++ b/public/downloads/AraComputational2022.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>HO</t>
   </si>
   <si>
-    <t>O</t>
+    <t>HOO</t>
   </si>
   <si>
-    <t>HOO</t>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>192</v>
       </c>
       <c r="N3" s="5">
-        <v>2114.502753734589</v>
+        <v>2114502.753734589</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03706207830849541</v>
+        <v>37.06207830849541</v>
       </c>
       <c r="P3" s="5">
         <v>57053</v>
@@ -709,10 +732,10 @@
         <v>192</v>
       </c>
       <c r="N4" s="5">
-        <v>2350.115448236465</v>
+        <v>2350115.448236465</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06454587883099329</v>
+        <v>64.54587883099329</v>
       </c>
       <c r="P4" s="5">
         <v>36410</v>
@@ -759,10 +782,10 @@
         <v>192</v>
       </c>
       <c r="N5" s="5">
-        <v>3749.24027633667</v>
+        <v>3749240.27633667</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1521113387023965</v>
+        <v>152.1113387023966</v>
       </c>
       <c r="P5" s="5">
         <v>24648</v>
@@ -809,10 +832,10 @@
         <v>192</v>
       </c>
       <c r="N6" s="5">
-        <v>3487.340958118439</v>
+        <v>3487340.958118439</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08743270716839088</v>
+        <v>87.43270716839088</v>
       </c>
       <c r="P6" s="5">
         <v>39886</v>
@@ -859,10 +882,10 @@
         <v>192</v>
       </c>
       <c r="N7" s="5">
-        <v>3700.327105760574</v>
+        <v>3700327.105760574</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1834115046225811</v>
+        <v>183.4115046225811</v>
       </c>
       <c r="P7" s="5">
         <v>20175</v>
@@ -909,10 +932,10 @@
         <v>192</v>
       </c>
       <c r="N8" s="5">
-        <v>543.9998836517334</v>
+        <v>543999.8836517334</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01865121142564314</v>
+        <v>18.65121142564314</v>
       </c>
       <c r="P8" s="5">
         <v>29167</v>
@@ -959,10 +982,10 @@
         <v>192</v>
       </c>
       <c r="N9" s="5">
-        <v>1365.505386352539</v>
+        <v>1365505.386352539</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03336359915833999</v>
+        <v>33.36359915833999</v>
       </c>
       <c r="P9" s="5">
         <v>40928</v>
@@ -1009,10 +1032,10 @@
         <v>192</v>
       </c>
       <c r="N10" s="5">
-        <v>2084.169105052948</v>
+        <v>2084169.105052948</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08690555854611576</v>
+        <v>86.90555854611576</v>
       </c>
       <c r="P10" s="5">
         <v>23982</v>
@@ -1059,10 +1082,10 @@
         <v>192</v>
       </c>
       <c r="N11" s="5">
-        <v>1051.183613300323</v>
+        <v>1051183.613300323</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04420452537007247</v>
+        <v>44.20452537007247</v>
       </c>
       <c r="P11" s="5">
         <v>23780</v>
@@ -1109,10 +1132,10 @@
         <v>192</v>
       </c>
       <c r="N12" s="5">
-        <v>539.4323272705078</v>
+        <v>539432.3272705078</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02332579465841511</v>
+        <v>23.32579465841511</v>
       </c>
       <c r="P12" s="5">
         <v>23126</v>
@@ -1159,10 +1182,10 @@
         <v>192</v>
       </c>
       <c r="N13" s="5">
-        <v>3100.241493463516</v>
+        <v>3100241.493463516</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07628359276256776</v>
+        <v>76.28359276256775</v>
       </c>
       <c r="P13" s="5">
         <v>40641</v>
@@ -1209,10 +1232,10 @@
         <v>192</v>
       </c>
       <c r="N14" s="5">
-        <v>5787.06995344162</v>
+        <v>5787069.95344162</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2434815699024579</v>
+        <v>243.4815699024579</v>
       </c>
       <c r="P14" s="5">
         <v>23768</v>
@@ -1259,10 +1282,10 @@
         <v>192</v>
       </c>
       <c r="N15" s="5">
-        <v>5082.06947517395</v>
+        <v>5082069.47517395</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2527009833013749</v>
+        <v>252.7009833013749</v>
       </c>
       <c r="P15" s="5">
         <v>20111</v>
@@ -1309,10 +1332,10 @@
         <v>192</v>
       </c>
       <c r="N16" s="5">
-        <v>2364.266536474228</v>
+        <v>2364266.536474228</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1053219233996003</v>
+        <v>105.3219233996003</v>
       </c>
       <c r="P16" s="5">
         <v>22448</v>
@@ -1359,10 +1382,10 @@
         <v>192</v>
       </c>
       <c r="N17" s="5">
-        <v>3116.447954654694</v>
+        <v>3116447.954654694</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1067130514537287</v>
+        <v>106.7130514537287</v>
       </c>
       <c r="P17" s="5">
         <v>29204</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4243483195417669</v>
+        <v>0.6778794858545915</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3186954869483375</v>
+        <v>0.5935659910004625</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3852461911596575</v>
+        <v>0.7688124610454488</v>
       </c>
       <c r="E3" s="4">
-        <v>94.99149659863936</v>
+        <v>93.79145408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>87.02705536912802</v>
+        <v>82.87384647651007</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7130465726328102</v>
+      </c>
+      <c r="O3" s="5">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5668498010017486</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4914868155991595</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
         <v>1</v>
       </c>
-      <c r="L3" s="5">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5842789152555428</v>
+        <v>0.8447348839547373</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5134048842946415</v>
+        <v>0.5928516341624629</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5687907266870664</v>
+        <v>1.07572341115599</v>
       </c>
       <c r="E4" s="4">
-        <v>96.10597363945577</v>
+        <v>90.85299744897968</v>
       </c>
       <c r="F4" s="4">
-        <v>89.5564177852349</v>
+        <v>75.60297818791946</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.8927313676963633</v>
+      </c>
+      <c r="O4" s="5">
+        <v>39</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.796026340214369</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6048734366198549</v>
+      </c>
+      <c r="R4" s="5">
+        <v>37</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.712799288553863</v>
+        <v>0.9719851978457195</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4673268601369176</v>
+        <v>0.5206282748592558</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4888949666465526</v>
+        <v>1.020781039257785</v>
       </c>
       <c r="E5" s="4">
-        <v>94.61256377551017</v>
+        <v>94.0577168367347</v>
       </c>
       <c r="F5" s="4">
-        <v>84.70724972035828</v>
+        <v>81.79530201342276</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.8468864625034654</v>
+      </c>
+      <c r="O5" s="5">
+        <v>52</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9680729191760813</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7673180748055789</v>
+      </c>
+      <c r="R5" s="5">
+        <v>49</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.057983922474519</v>
+        <v>1.009932837593625</v>
       </c>
       <c r="C3" s="4">
-        <v>0.403496220414617</v>
+        <v>0.9946840431082778</v>
       </c>
       <c r="D3" s="4">
-        <v>1.13249176592178</v>
+        <v>1.021458896335105</v>
       </c>
       <c r="E3" s="4">
-        <v>93.55070153061222</v>
+        <v>90.10150935374152</v>
       </c>
       <c r="F3" s="4">
-        <v>82.33763282997627</v>
+        <v>79.35647371364641</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.061029127043414</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4886453862085142</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4441892666045186</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.320862723939082</v>
+        <v>1.643066006422165</v>
       </c>
       <c r="C4" s="4">
-        <v>0.536851955997264</v>
+        <v>1.246522736488108</v>
       </c>
       <c r="D4" s="4">
-        <v>1.369099429964228</v>
+        <v>1.490933127208385</v>
       </c>
       <c r="E4" s="4">
-        <v>94.91602891156464</v>
+        <v>86.0055272108844</v>
       </c>
       <c r="F4" s="4">
-        <v>86.3277754474273</v>
+        <v>68.03499021252802</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M4" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>9</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.696383812906371</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.282028587060316</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6078166474813875</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.222866187685896</v>
+        <v>1.568142363120584</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5839478303506953</v>
+        <v>1.2979412036548</v>
       </c>
       <c r="D5" s="4">
-        <v>1.278536180339671</v>
+        <v>1.583705563801124</v>
       </c>
       <c r="E5" s="4">
-        <v>93.99234693877551</v>
+        <v>90.50116921768706</v>
       </c>
       <c r="F5" s="4">
-        <v>83.65142617449682</v>
+        <v>76.80945889261764</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.678105544845076</v>
+      </c>
+      <c r="O5" s="5">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.770678926066161</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5455872021909621</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4934339149005135</v>
+        <v>0.4243483195417669</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4260099913828674</v>
+        <v>0.3186954869483375</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5176489689011452</v>
+        <v>0.3852461911596575</v>
       </c>
       <c r="E3" s="4">
-        <v>96.40518707482985</v>
+        <v>94.99149659863936</v>
       </c>
       <c r="F3" s="4">
-        <v>87.80480984340068</v>
+        <v>87.02705536912802</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1790374909568283</v>
+      </c>
+      <c r="O3" s="5">
+        <v>55</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3529583569173227</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2505888739279591</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7866587994896898</v>
+        <v>0.712799288553863</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4362966685526762</v>
+        <v>0.4673268601369176</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8487244524102651</v>
+        <v>0.4888949666465526</v>
       </c>
       <c r="E4" s="4">
-        <v>97.53188775510205</v>
+        <v>94.61256377551017</v>
       </c>
       <c r="F4" s="4">
-        <v>90.71431068232636</v>
+        <v>84.70724972035828</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>11</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3235413195161727</v>
+      </c>
+      <c r="O4" s="5">
+        <v>54</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5523744423840238</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.32230351072836</v>
+      </c>
+      <c r="R4" s="5">
+        <v>53</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8366066691075142</v>
+        <v>0.5842789152555428</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3945108787639171</v>
+        <v>0.5134048842946415</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9169318586114344</v>
+        <v>0.5687907266870664</v>
       </c>
       <c r="E5" s="4">
-        <v>96.04007227891157</v>
+        <v>96.10597363945577</v>
       </c>
       <c r="F5" s="4">
-        <v>87.44232382550457</v>
+        <v>89.5564177852349</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
         <v>3</v>
-      </c>
-      <c r="J5" s="5">
-        <v>15</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2132845692141044</v>
+      </c>
+      <c r="O5" s="5">
+        <v>60</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5161011729185602</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4358343744847943</v>
+      </c>
+      <c r="R5" s="5">
+        <v>59</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8399564892888794</v>
+        <v>1.057983922474519</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5537939694007328</v>
+        <v>0.403496220414617</v>
       </c>
       <c r="D3" s="4">
-        <v>1.013987111887535</v>
+        <v>1.13249176592178</v>
       </c>
       <c r="E3" s="4">
-        <v>94.27561649659835</v>
+        <v>93.55070153061222</v>
       </c>
       <c r="F3" s="4">
-        <v>84.09902824384858</v>
+        <v>82.33763282997627</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M3" s="5">
+        <v>8</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.8800386901990487</v>
+      </c>
+      <c r="O3" s="5">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.919975553390493</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5547109532503978</v>
+      </c>
+      <c r="R3" s="5">
+        <v>41</v>
+      </c>
+      <c r="S3" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.316812168743336</v>
+        <v>1.222866187685896</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6932707243865092</v>
+        <v>0.5839478303506953</v>
       </c>
       <c r="D4" s="4">
-        <v>1.492007738350574</v>
+        <v>1.278536180339671</v>
       </c>
       <c r="E4" s="4">
-        <v>94.45897108843533</v>
+        <v>93.99234693877551</v>
       </c>
       <c r="F4" s="4">
-        <v>84.17313338926192</v>
+        <v>83.65142617449682</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>12</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.194751372003503</v>
+      </c>
+      <c r="O4" s="5">
+        <v>51</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.084181267634807</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8622284025363476</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.312218198951232</v>
+        <v>1.320862723939082</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6484369314571505</v>
+        <v>0.536851955997264</v>
       </c>
       <c r="D5" s="4">
-        <v>1.436805041312813</v>
+        <v>1.369099429964228</v>
       </c>
       <c r="E5" s="4">
-        <v>91.89253826530654</v>
+        <v>94.91602891156464</v>
       </c>
       <c r="F5" s="4">
-        <v>77.16670162192518</v>
+        <v>86.3277754474273</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>23</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>11</v>
+      </c>
+      <c r="M5" s="5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
-        <v>17</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>10</v>
+      <c r="N5" s="4">
+        <v>1.162286996974362</v>
+      </c>
+      <c r="O5" s="5">
+        <v>52</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.148377284845395</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8034795681356607</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,34 +2697,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2387288188195049</v>
+        <v>0.4934339149005135</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1848788219270191</v>
+        <v>0.4260099913828674</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2368989423359457</v>
+        <v>0.5176489689011452</v>
       </c>
       <c r="E3" s="4">
-        <v>96.42963435374149</v>
+        <v>96.40518707482985</v>
       </c>
       <c r="F3" s="4">
-        <v>88.81012304250609</v>
+        <v>87.80480984340068</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
         <v>5</v>
@@ -2353,91 +2756,145 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2782070042260623</v>
+      </c>
+      <c r="O3" s="5">
+        <v>54</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4989382052298792</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.432562834828403</v>
+      </c>
+      <c r="R3" s="5">
+        <v>53</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4101441022800613</v>
+        <v>0.8366066691075142</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3973875385782038</v>
+        <v>0.3945108787639171</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4571048245744533</v>
+        <v>0.9169318586114344</v>
       </c>
       <c r="E4" s="4">
-        <v>96.8920068027211</v>
+        <v>96.04007227891157</v>
       </c>
       <c r="F4" s="4">
-        <v>90.90132130872495</v>
+        <v>87.44232382550457</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>4</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6136638985816594</v>
+      </c>
+      <c r="O4" s="5">
+        <v>56</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9050294696833273</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7687924275991252</v>
+      </c>
+      <c r="R4" s="5">
+        <v>51</v>
+      </c>
+      <c r="S4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5258112463285654</v>
+        <v>0.7866587994896898</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2924878272646868</v>
+        <v>0.4362966685526762</v>
       </c>
       <c r="D5" s="4">
-        <v>0.313112528196867</v>
+        <v>0.8487244524102651</v>
       </c>
       <c r="E5" s="4">
-        <v>95.04357993197279</v>
+        <v>97.53188775510205</v>
       </c>
       <c r="F5" s="4">
-        <v>84.98951342281885</v>
+        <v>90.71431068232636</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>11</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>4</v>
       </c>
-      <c r="J5" s="5">
-        <v>9</v>
-      </c>
-      <c r="K5" s="5">
-        <v>3</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.5369695497644357</v>
+      </c>
+      <c r="O5" s="5">
+        <v>59</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8167869444095512</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6132195809269937</v>
+      </c>
+      <c r="R5" s="5">
+        <v>54</v>
+      </c>
+      <c r="S5" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4245105501831989</v>
+        <v>0.8399564892888794</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3264596582754796</v>
+        <v>0.5537939694007328</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5142334764436705</v>
+        <v>1.013987111887535</v>
       </c>
       <c r="E3" s="4">
-        <v>97.36979166666666</v>
+        <v>94.27561649659835</v>
       </c>
       <c r="F3" s="4">
-        <v>90.843645134228</v>
+        <v>84.09902824384858</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7840541456704667</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6930207737133075</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5949409141917382</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5487572286503832</v>
+        <v>1.312218198951232</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2438480709482617</v>
+        <v>0.6484369314571505</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5069013592245919</v>
+        <v>1.436805041312813</v>
       </c>
       <c r="E4" s="4">
-        <v>98.01870748299321</v>
+        <v>91.89253826530654</v>
       </c>
       <c r="F4" s="4">
-        <v>92.67232941834455</v>
+        <v>77.16670162192518</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
+        <v>35</v>
+      </c>
+      <c r="I4" s="5">
+        <v>12</v>
+      </c>
+      <c r="J4" s="5">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.187756106315856</v>
+      </c>
+      <c r="O4" s="5">
+        <v>45</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.023942865462487</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7559524592722544</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="B5" s="4">
-        <v>0.8253833572835072</v>
+        <v>1.316812168743336</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5699582395154694</v>
+        <v>0.6932707243865092</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9044581594585298</v>
+        <v>1.492007738350574</v>
       </c>
       <c r="E5" s="4">
-        <v>95.4187925170073</v>
+        <v>94.45897108843533</v>
       </c>
       <c r="F5" s="4">
-        <v>87.30984340044918</v>
+        <v>84.17313338926192</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K5" s="5">
         <v>2</v>
       </c>
       <c r="L5" s="5">
+        <v>10</v>
+      </c>
+      <c r="M5" s="5">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.247213572259313</v>
+      </c>
+      <c r="O5" s="5">
+        <v>48</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.005984222359067</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7036440639182364</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
         <v>4</v>
       </c>
-      <c r="M5" s="5">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2356466474794726</v>
+        <v>0.2387288188195049</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1683748609091564</v>
+        <v>0.1848788219270191</v>
       </c>
       <c r="D3" s="4">
-        <v>0.208014828536436</v>
+        <v>0.2368989423359457</v>
       </c>
       <c r="E3" s="4">
-        <v>94.69759778911566</v>
+        <v>96.42963435374149</v>
       </c>
       <c r="F3" s="4">
-        <v>85.90778803132007</v>
+        <v>88.81012304250609</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08963091676242503</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2171080173445042</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1633704386971049</v>
+      </c>
+      <c r="R3" s="5">
+        <v>56</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.318793586523906</v>
+        <v>0.5258112463285654</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2674394066183386</v>
+        <v>0.2924878272646868</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3003604133627425</v>
+        <v>0.313112528196867</v>
       </c>
       <c r="E4" s="4">
-        <v>95.45758928571425</v>
+        <v>95.04357993197279</v>
       </c>
       <c r="F4" s="4">
-        <v>87.83609479865834</v>
+        <v>84.98951342281885</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
         <v>6</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1881153155310177</v>
+      </c>
+      <c r="O4" s="5">
+        <v>51</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4581759911648445</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2481861045267076</v>
+      </c>
+      <c r="R4" s="5">
+        <v>51</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4466974138185631</v>
+        <v>0.4101441022800613</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2626697244664237</v>
+        <v>0.3973875385782038</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2614408129671139</v>
+        <v>0.4571048245744533</v>
       </c>
       <c r="E5" s="4">
-        <v>93.24032738095237</v>
+        <v>96.8920068027211</v>
       </c>
       <c r="F5" s="4">
-        <v>81.08763282997755</v>
+        <v>90.90132130872495</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
         <v>1</v>
       </c>
-      <c r="L5" s="5">
-        <v>11</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
+      <c r="N5" s="4">
+        <v>-0.2516221627271897</v>
+      </c>
+      <c r="O5" s="5">
+        <v>60</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3432093397403266</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3114191807300002</v>
+      </c>
+      <c r="R5" s="5">
+        <v>59</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,132 +3597,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7527630090851096</v>
+        <v>0.4245105501831989</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3946968473091494</v>
+        <v>0.3264596582754796</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9274466697018167</v>
+        <v>0.5142334764436705</v>
       </c>
       <c r="E3" s="4">
-        <v>96.53911564625849</v>
+        <v>97.36979166666666</v>
       </c>
       <c r="F3" s="4">
-        <v>87.93449384787523</v>
+        <v>90.843645134228</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="5">
-        <v>13</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
       <c r="M3" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1687291093951412</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3361167581606996</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2124096892155558</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9398874322589744</v>
+        <v>0.8253833572835072</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3070774167753856</v>
+        <v>0.5699582395154694</v>
       </c>
       <c r="D4" s="4">
-        <v>1.050021330126954</v>
+        <v>0.9044581594585298</v>
       </c>
       <c r="E4" s="4">
-        <v>96.56462585034015</v>
+        <v>95.4187925170073</v>
       </c>
       <c r="F4" s="4">
-        <v>88.39188338926176</v>
+        <v>87.30984340044918</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
         <v>4</v>
       </c>
-      <c r="J4" s="5">
-        <v>15</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
       <c r="M4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.01604855497318088</v>
+      </c>
+      <c r="O4" s="5">
+        <v>52</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8178605971398287</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5579218232855837</v>
+      </c>
+      <c r="R4" s="5">
+        <v>48</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9622610549925886</v>
+        <v>0.5487572286503832</v>
       </c>
       <c r="C5" s="4">
-        <v>0.472052891280182</v>
+        <v>0.2438480709482617</v>
       </c>
       <c r="D5" s="4">
-        <v>1.061704029400894</v>
+        <v>0.5069013592245919</v>
       </c>
       <c r="E5" s="4">
-        <v>96.0815263605444</v>
+        <v>98.01870748299321</v>
       </c>
       <c r="F5" s="4">
-        <v>87.17037192393666</v>
+        <v>92.67232941834455</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>10</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1827495203971199</v>
+      </c>
+      <c r="O5" s="5">
+        <v>60</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6384068399364047</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3984337813526177</v>
+      </c>
+      <c r="R5" s="5">
+        <v>55</v>
+      </c>
+      <c r="S5" s="5">
         <v>5</v>
       </c>
-      <c r="J5" s="5">
-        <v>13</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>7</v>
-      </c>
-      <c r="M5" s="5">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2356466474794726</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1683748609091564</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.208014828536436</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.69759778911566</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.90778803132007</v>
+      </c>
+      <c r="G3" s="5">
+        <v>64</v>
+      </c>
+      <c r="H3" s="5">
+        <v>54</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.02145925383666704</v>
+      </c>
+      <c r="O3" s="5">
+        <v>55</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2351552217061387</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1685872175421188</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4466974138185631</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2626697244664237</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2614408129671139</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.24032738095237</v>
+      </c>
+      <c r="F4" s="4">
+        <v>81.08763282997755</v>
+      </c>
+      <c r="G4" s="5">
+        <v>64</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>12</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.131296056778872</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4309949533725967</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2294618663124265</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.318793586523906</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2674394066183386</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3003604133627425</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.45758928571425</v>
+      </c>
+      <c r="F5" s="4">
+        <v>87.83609479865834</v>
+      </c>
+      <c r="G5" s="5">
+        <v>64</v>
+      </c>
+      <c r="H5" s="5">
+        <v>56</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>8</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.05913518391144909</v>
+      </c>
+      <c r="O5" s="5">
+        <v>57</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3290099045310935</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2736832335635749</v>
+      </c>
+      <c r="R5" s="5">
+        <v>56</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7527630090851096</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3946968473091494</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9274466697018167</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.53911564625849</v>
+      </c>
+      <c r="F3" s="4">
+        <v>87.93449384787523</v>
+      </c>
+      <c r="G3" s="5">
+        <v>64</v>
+      </c>
+      <c r="H3" s="5">
+        <v>47</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5">
+        <v>13</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>6</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2613181096570754</v>
+      </c>
+      <c r="O3" s="5">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8551231335009826</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6468840139789233</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.9622610549925886</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.472052891280182</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.061704029400894</v>
+      </c>
+      <c r="E4" s="4">
+        <v>96.0815263605444</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.17037192393666</v>
+      </c>
+      <c r="G4" s="5">
+        <v>64</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5">
+        <v>13</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>5</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2652448560984837</v>
+      </c>
+      <c r="O4" s="5">
+        <v>51</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.028471441325691</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6718907647985274</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.9398874322589744</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3070774167753856</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.050021330126954</v>
+      </c>
+      <c r="E5" s="4">
+        <v>96.56462585034015</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.39188338926176</v>
+      </c>
+      <c r="G5" s="5">
+        <v>64</v>
+      </c>
+      <c r="H5" s="5">
+        <v>45</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2873073210433201</v>
+      </c>
+      <c r="O5" s="5">
+        <v>52</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.026065459920642</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5950428411525783</v>
+      </c>
+      <c r="R5" s="5">
+        <v>47</v>
+      </c>
+      <c r="S5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>48.4375</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.770833333333333</v>
+      </c>
+      <c r="D3" s="3">
+        <v>44.79166666666667</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F3" s="3">
+        <v>39.58333333333333</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.003233611525728</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.6290038801359723</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.8898350282420524</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.38679846938778</v>
+      </c>
+      <c r="L3" s="4">
+        <v>70.35759228187972</v>
+      </c>
+      <c r="M3" s="5">
+        <v>192</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2114502.753734589</v>
+      </c>
+      <c r="O3" s="4">
+        <v>37.06207830849541</v>
+      </c>
+      <c r="P3" s="5">
+        <v>57053</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>67.70833333333334</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="D4" s="3">
+        <v>28.64583333333333</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F4" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4.6875</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.7817919373302517</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.563787646102885</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.6065695373071569</v>
+      </c>
+      <c r="K4" s="4">
+        <v>89.72027352607695</v>
+      </c>
+      <c r="L4" s="4">
+        <v>78.78617869127491</v>
+      </c>
+      <c r="M4" s="5">
+        <v>192</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2350115.448236465</v>
+      </c>
+      <c r="O4" s="4">
+        <v>64.54587883099329</v>
+      </c>
+      <c r="P4" s="5">
+        <v>36410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>76.5625</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4.6875</v>
+      </c>
+      <c r="D5" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F5" s="3">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.025044931378842</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.7923443318874139</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.066350117528539</v>
+      </c>
+      <c r="K5" s="4">
+        <v>95.84449404761904</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.15050568605446</v>
+      </c>
+      <c r="M5" s="5">
+        <v>192</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3749240.27633667</v>
+      </c>
+      <c r="O5" s="4">
+        <v>152.1113387023966</v>
+      </c>
+      <c r="P5" s="5">
+        <v>24648</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>72.39583333333334</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D6" s="3">
+        <v>23.4375</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17.1875</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.7366094342142514</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.43648936203786</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.5504762921307507</v>
+      </c>
+      <c r="K6" s="4">
+        <v>91.00340136054443</v>
+      </c>
+      <c r="L6" s="4">
+        <v>78.65754334451861</v>
+      </c>
+      <c r="M6" s="5">
+        <v>192</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3487340.958118439</v>
+      </c>
+      <c r="O6" s="4">
+        <v>87.43270716839088</v>
+      </c>
+      <c r="P6" s="5">
+        <v>39886</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>81.77083333333334</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.604166666666667</v>
+      </c>
+      <c r="D7" s="3">
+        <v>15.625</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.9702441939570171</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.7595440448405081</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.000430152114304</v>
+      </c>
+      <c r="K7" s="4">
+        <v>97.2006094104308</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.18130126771139</v>
+      </c>
+      <c r="M7" s="5">
+        <v>192</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3700327.105760574</v>
+      </c>
+      <c r="O7" s="4">
+        <v>183.4115046225811</v>
+      </c>
+      <c r="P7" s="5">
+        <v>20175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>71.875</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10.41666666666667</v>
+      </c>
+      <c r="D8" s="3">
+        <v>17.70833333333334</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.5208333333333333</v>
+      </c>
+      <c r="F8" s="3">
+        <v>14.0625</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7769830201307331</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.6198276610982919</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.8277863007810878</v>
+      </c>
+      <c r="K8" s="4">
+        <v>92.90072278911578</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.09070889261666</v>
+      </c>
+      <c r="M8" s="5">
+        <v>192</v>
+      </c>
+      <c r="N8" s="5">
+        <v>543999.8836517334</v>
+      </c>
+      <c r="O8" s="4">
+        <v>18.65121142564314</v>
+      </c>
+      <c r="P8" s="5">
+        <v>29167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>66.14583333333334</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7.8125</v>
+      </c>
+      <c r="D9" s="3">
+        <v>26.04166666666667</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="F9" s="3">
+        <v>21.35416666666666</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.8471176331116638</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5244134201202187</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6390875361240212</v>
+      </c>
+      <c r="K9" s="4">
+        <v>88.86940192743762</v>
+      </c>
+      <c r="L9" s="4">
+        <v>74.73364093959732</v>
+      </c>
+      <c r="M9" s="5">
+        <v>192</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1365505.386352539</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.36359915833999</v>
+      </c>
+      <c r="P9" s="5">
+        <v>40928</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>86.45833333333334</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.895833333333332</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6.770833333333333</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4738113240733022</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3393259840681671</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.4034397655824717</v>
+      </c>
+      <c r="K10" s="4">
+        <v>95.23667800453514</v>
+      </c>
+      <c r="L10" s="4">
+        <v>87.09690762490771</v>
+      </c>
+      <c r="M10" s="5">
+        <v>192</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2084169.105052948</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.90555854611576</v>
+      </c>
+      <c r="P10" s="5">
+        <v>23982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>68.22916666666666</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4.6875</v>
+      </c>
+      <c r="D11" s="3">
+        <v>27.08333333333333</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.5208333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G11" s="3">
+        <v>9.895833333333332</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.050844701956898</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.7462500503657051</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.092960240325064</v>
+      </c>
+      <c r="K11" s="4">
+        <v>94.15302579365077</v>
+      </c>
+      <c r="L11" s="4">
+        <v>84.10561148396702</v>
+      </c>
+      <c r="M11" s="5">
+        <v>192</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1051183.613300323</v>
+      </c>
+      <c r="O11" s="4">
+        <v>44.20452537007247</v>
+      </c>
+      <c r="P11" s="5">
+        <v>23780</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>82.29166666666666</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5.208333333333334</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5.729166666666666</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.729166666666666</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.7402515397742526</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.6028360849589771</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.7923833969233</v>
+      </c>
+      <c r="K12" s="4">
+        <v>96.65904903628119</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.65381478374393</v>
+      </c>
+      <c r="M12" s="5">
+        <v>192</v>
+      </c>
+      <c r="N12" s="5">
+        <v>539432.3272705078</v>
+      </c>
+      <c r="O12" s="4">
+        <v>23.32579465841511</v>
+      </c>
+      <c r="P12" s="5">
+        <v>23126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>70.3125</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9.375</v>
+      </c>
+      <c r="D13" s="3">
+        <v>20.3125</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="F13" s="3">
+        <v>13.02083333333333</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.9076492871782872</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.6816552477208353</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.9860543141725202</v>
+      </c>
+      <c r="K13" s="4">
+        <v>93.54237528344734</v>
+      </c>
+      <c r="L13" s="4">
+        <v>81.81295441834563</v>
+      </c>
+      <c r="M13" s="5">
+        <v>192</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3100241.493463516</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.28359276256775</v>
+      </c>
+      <c r="P13" s="5">
+        <v>40641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>86.45833333333334</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9.895833333333332</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6.770833333333333</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3394977827498918</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2420479973552408</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2907678317909027</v>
+      </c>
+      <c r="K14" s="4">
+        <v>96.12174036281176</v>
+      </c>
+      <c r="L14" s="4">
+        <v>88.23365259135035</v>
+      </c>
+      <c r="M14" s="5">
+        <v>192</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5787069.95344162</v>
+      </c>
+      <c r="O14" s="4">
+        <v>243.4815699024579</v>
+      </c>
+      <c r="P14" s="5">
+        <v>23768</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>5.208333333333334</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5974613984123111</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3800091111086792</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.6412784606711187</v>
+      </c>
+      <c r="K15" s="4">
+        <v>96.9357638888893</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.27527265100805</v>
+      </c>
+      <c r="M15" s="5">
+        <v>192</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5082069.47517395</v>
+      </c>
+      <c r="O15" s="4">
+        <v>252.7009833013749</v>
+      </c>
+      <c r="P15" s="5">
+        <v>20111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15.10416666666667</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="F16" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3317200265366096</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2242642094692707</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2514901336086094</v>
+      </c>
+      <c r="K16" s="4">
+        <v>94.46517148526091</v>
+      </c>
+      <c r="L16" s="4">
+        <v>84.94383855331853</v>
+      </c>
+      <c r="M16" s="5">
+        <v>192</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2364266.536474228</v>
+      </c>
+      <c r="O16" s="4">
+        <v>105.3219233996003</v>
+      </c>
+      <c r="P16" s="5">
+        <v>22448</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>74.47916666666666</v>
+      </c>
+      <c r="C17" s="3">
+        <v>6.770833333333333</v>
+      </c>
+      <c r="D17" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="F17" s="3">
+        <v>9.895833333333332</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6.770833333333333</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.969886678249105</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.6380643088438406</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.085070782117644</v>
+      </c>
+      <c r="K17" s="4">
+        <v>96.39508928571465</v>
+      </c>
+      <c r="L17" s="4">
+        <v>87.8322497203575</v>
+      </c>
+      <c r="M17" s="5">
+        <v>192</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3116447.954654694</v>
+      </c>
+      <c r="O17" s="4">
+        <v>106.7130514537287</v>
+      </c>
+      <c r="P17" s="5">
+        <v>29204</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3250,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -3294,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3338,16 +5514,16 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3382,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3429,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3470,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" s="5">
         <v>29</v>
@@ -3479,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3514,10 +5690,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -3561,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3602,10 +5778,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3646,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="K13" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3693,13 +5869,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3737,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -3787,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3822,16 +5998,16 @@
         <v>2</v>
       </c>
       <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>14</v>
+      </c>
+      <c r="M17" s="5">
         <v>1</v>
       </c>
-      <c r="L17" s="5">
-        <v>15</v>
-      </c>
-      <c r="M17" s="5">
-        <v>3</v>
-      </c>
       <c r="N17" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5">
+        <v>86</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>76</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>35</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>130</v>
+      </c>
+      <c r="C4" s="5">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5">
+        <v>55</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>44</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>24</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>147</v>
+      </c>
+      <c r="C5" s="5">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5">
+        <v>36</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>17</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>139</v>
+      </c>
+      <c r="C6" s="5">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5">
+        <v>33</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8</v>
+      </c>
+      <c r="I6" s="5">
+        <v>8</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>19</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>157</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5">
+        <v>14</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>8</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>138</v>
+      </c>
+      <c r="C8" s="5">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5">
+        <v>34</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>27</v>
+      </c>
+      <c r="G8" s="5">
+        <v>6</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>17</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>127</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5">
+        <v>50</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>41</v>
+      </c>
+      <c r="G9" s="5">
+        <v>6</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>29</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>166</v>
+      </c>
+      <c r="C10" s="5">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3</v>
+      </c>
+      <c r="F10" s="5">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5">
+        <v>3</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>13</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>131</v>
+      </c>
+      <c r="C11" s="5">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>32</v>
+      </c>
+      <c r="G11" s="5">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>24</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>158</v>
+      </c>
+      <c r="C12" s="5">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5">
+        <v>24</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5">
+        <v>11</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>8</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>135</v>
+      </c>
+      <c r="C13" s="5">
+        <v>18</v>
+      </c>
+      <c r="D13" s="5">
+        <v>39</v>
+      </c>
+      <c r="E13" s="5">
+        <v>6</v>
+      </c>
+      <c r="F13" s="5">
+        <v>25</v>
+      </c>
+      <c r="G13" s="5">
+        <v>8</v>
+      </c>
+      <c r="H13" s="5">
+        <v>6</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>15</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>166</v>
+      </c>
+      <c r="C14" s="5">
+        <v>7</v>
+      </c>
+      <c r="D14" s="5">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5">
+        <v>4</v>
+      </c>
+      <c r="F14" s="5">
+        <v>13</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>5</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>160</v>
+      </c>
+      <c r="C15" s="5">
+        <v>8</v>
+      </c>
+      <c r="D15" s="5">
+        <v>24</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5">
+        <v>2</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>6</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>156</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5">
+        <v>29</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5">
+        <v>24</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>3</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>13</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>143</v>
+      </c>
+      <c r="C17" s="5">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5">
+        <v>36</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4</v>
+      </c>
+      <c r="F17" s="5">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5">
+        <v>4</v>
+      </c>
+      <c r="I17" s="5">
+        <v>2</v>
+      </c>
+      <c r="J17" s="5">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>14</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.19079174316359</v>
@@ -3960,91 +6923,145 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.7795812446487741</v>
+      </c>
+      <c r="O3" s="5">
+        <v>32</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7868286216861956</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3922330359307251</v>
+      </c>
+      <c r="R3" s="5">
+        <v>31</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.775503561078585</v>
+        <v>1.587892086274354</v>
       </c>
       <c r="C4" s="4">
-        <v>0.844038099226216</v>
+        <v>1.020853297869371</v>
       </c>
       <c r="D4" s="4">
-        <v>1.857279120656329</v>
+        <v>1.639847674070492</v>
       </c>
       <c r="E4" s="4">
-        <v>88.53528911564624</v>
+        <v>86.34566326530613</v>
       </c>
       <c r="F4" s="4">
-        <v>71.80473993288605</v>
+        <v>68.46266778523513</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
         <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M4" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.538513566617478</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.048511152901003</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6665757316990029</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.587892086274354</v>
+        <v>1.775503561078585</v>
       </c>
       <c r="C5" s="4">
-        <v>1.020853297869371</v>
+        <v>0.844038099226216</v>
       </c>
       <c r="D5" s="4">
-        <v>1.639847674070492</v>
+        <v>1.857279120656329</v>
       </c>
       <c r="E5" s="4">
-        <v>86.34566326530613</v>
+        <v>88.53528911564624</v>
       </c>
       <c r="F5" s="4">
-        <v>68.46266778523513</v>
+        <v>71.80473993288605</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5">
         <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M5" s="5">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.985547438153483</v>
+      </c>
+      <c r="O5" s="5">
+        <v>31</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.174361059989987</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8521476344195503</v>
+      </c>
+      <c r="R5" s="5">
+        <v>27</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.040346194032367</v>
@@ -4173,91 +7223,145 @@
       <c r="M3" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.9748091222858898</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.650361487585953</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5708269785345039</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.672619197243343</v>
+        <v>1.987024147040938</v>
       </c>
       <c r="C4" s="4">
-        <v>1.13083318827921</v>
+        <v>1.462627533761888</v>
       </c>
       <c r="D4" s="4">
-        <v>1.659574934659723</v>
+        <v>2.007846513578413</v>
       </c>
       <c r="E4" s="4">
-        <v>90.90508078231289</v>
+        <v>87.74553571428571</v>
       </c>
       <c r="F4" s="4">
-        <v>79.07141359060429</v>
+        <v>75.76342281879189</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M4" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.049461377170462</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9127790199725443</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4629920204068526</v>
+      </c>
+      <c r="R4" s="5">
+        <v>39</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.987024147040938</v>
+        <v>1.672619197243343</v>
       </c>
       <c r="C5" s="4">
-        <v>1.462627533761888</v>
+        <v>1.13083318827921</v>
       </c>
       <c r="D5" s="4">
-        <v>2.007846513578413</v>
+        <v>1.659574934659723</v>
       </c>
       <c r="E5" s="4">
-        <v>87.74553571428571</v>
+        <v>90.90508078231289</v>
       </c>
       <c r="F5" s="4">
-        <v>75.76342281879189</v>
+        <v>79.07141359060429</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
         <v>16</v>
       </c>
-      <c r="M5" s="5">
-        <v>20</v>
+      <c r="N5" s="4">
+        <v>1.655141997710326</v>
+      </c>
+      <c r="O5" s="5">
+        <v>46</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7822353044322575</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6491710297456453</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7464,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.746579466490198</v>
@@ -4386,91 +7523,145 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.398000250551454</v>
+      </c>
+      <c r="O3" s="5">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7577917781775221</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5422904777537053</v>
+      </c>
+      <c r="R3" s="5">
+        <v>50</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.379668195916819</v>
+        <v>1.005110415891309</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5392173297537906</v>
+        <v>0.3962547710911023</v>
       </c>
       <c r="D4" s="4">
-        <v>1.413515066071145</v>
+        <v>1.03233754130452</v>
       </c>
       <c r="E4" s="4">
-        <v>96.81388180272111</v>
+        <v>95.1163903061224</v>
       </c>
       <c r="F4" s="4">
-        <v>89.49297399328836</v>
+        <v>85.0367030201346</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
         <v>20</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>11</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7838972193724164</v>
+      </c>
+      <c r="O4" s="5">
+        <v>51</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.130290796946263</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9406114630275214</v>
+      </c>
+      <c r="R4" s="5">
+        <v>48</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.005110415891309</v>
+        <v>1.379668195916819</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3962547710911023</v>
+        <v>0.5392173297537906</v>
       </c>
       <c r="D5" s="4">
-        <v>1.03233754130452</v>
+        <v>1.413515066071145</v>
       </c>
       <c r="E5" s="4">
-        <v>95.1163903061224</v>
+        <v>96.81388180272111</v>
       </c>
       <c r="F5" s="4">
-        <v>85.0367030201346</v>
+        <v>89.49297399328836</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>20</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.183966738448005</v>
+      </c>
+      <c r="O5" s="5">
+        <v>57</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.187052219012742</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.902260054580481</v>
+      </c>
+      <c r="R5" s="5">
+        <v>49</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7764,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6205539788847563</v>
@@ -4599,91 +7823,145 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5958395602820948</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3911462275278442</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3420507307755912</v>
+      </c>
+      <c r="R3" s="5">
+        <v>51</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.00965066165438</v>
+        <v>1.272096405318071</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8944749433247289</v>
+        <v>0.843174128673123</v>
       </c>
       <c r="D4" s="4">
-        <v>1.009068462005545</v>
+        <v>1.073556869978903</v>
       </c>
       <c r="E4" s="4">
-        <v>91.80059523809523</v>
+        <v>89.09970238095261</v>
       </c>
       <c r="F4" s="4">
-        <v>80.91250699105154</v>
+        <v>74.31155620805427</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>23</v>
+      </c>
+      <c r="K4" s="5">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5">
+        <v>5</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.098444606099456</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.12436299610429</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4892464162241351</v>
+      </c>
+      <c r="R4" s="5">
+        <v>40</v>
+      </c>
+      <c r="S4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
-        <v>16</v>
-      </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>10</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.272096405318071</v>
+        <v>1.00965066165438</v>
       </c>
       <c r="C5" s="4">
-        <v>0.843174128673123</v>
+        <v>0.8944749433247289</v>
       </c>
       <c r="D5" s="4">
-        <v>1.073556869978903</v>
+        <v>1.009068462005545</v>
       </c>
       <c r="E5" s="4">
-        <v>89.09970238095261</v>
+        <v>91.80059523809523</v>
       </c>
       <c r="F5" s="4">
-        <v>74.31155620805427</v>
+        <v>80.91250699105154</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.9578985741430226</v>
+      </c>
+      <c r="O5" s="5">
+        <v>49</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6943190790106201</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4928661959321246</v>
+      </c>
+      <c r="R5" s="5">
+        <v>48</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8064,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.7629668015870665</v>
@@ -4812,91 +8123,145 @@
       <c r="M3" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5874900262169779</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8448886680353618</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6956149133391002</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.084520068474804</v>
+        <v>0.899416405959062</v>
       </c>
       <c r="C4" s="4">
-        <v>0.330432027289805</v>
+        <v>0.330320420803273</v>
       </c>
       <c r="D4" s="4">
-        <v>1.097184275045112</v>
+        <v>0.9772295631913083</v>
       </c>
       <c r="E4" s="4">
-        <v>97.79602465986387</v>
+        <v>97.07642431972783</v>
       </c>
       <c r="F4" s="4">
-        <v>91.31274468680125</v>
+        <v>90.09665128635341</v>
       </c>
       <c r="G4" s="5">
         <v>64</v>
       </c>
       <c r="H4" s="5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5">
         <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>13</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.8581304658900576</v>
+      </c>
+      <c r="O4" s="5">
+        <v>59</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9597961092371899</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8107434010541894</v>
+      </c>
+      <c r="R4" s="5">
+        <v>55</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.899416405959062</v>
+        <v>1.084520068474804</v>
       </c>
       <c r="C5" s="4">
-        <v>0.330320420803273</v>
+        <v>0.330432027289805</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9772295631913083</v>
+        <v>1.097184275045112</v>
       </c>
       <c r="E5" s="4">
-        <v>97.07642431972783</v>
+        <v>97.79602465986387</v>
       </c>
       <c r="F5" s="4">
-        <v>90.09665128635341</v>
+        <v>91.31274468680125</v>
       </c>
       <c r="G5" s="5">
         <v>64</v>
       </c>
       <c r="H5" s="5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.8818604746063728</v>
+      </c>
+      <c r="O5" s="5">
+        <v>55</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.1060478045985</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7727983887847495</v>
+      </c>
+      <c r="R5" s="5">
+        <v>48</v>
+      </c>
+      <c r="S5" s="5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6778794858545915</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5935659910004625</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7688124610454488</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.79145408163265</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.87384647651007</v>
-      </c>
-      <c r="G3" s="5">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5">
-        <v>50</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>12</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>9</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9719851978457195</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5206282748592558</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.020781039257785</v>
-      </c>
-      <c r="E4" s="4">
-        <v>94.0577168367347</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.79530201342276</v>
-      </c>
-      <c r="G4" s="5">
-        <v>64</v>
-      </c>
-      <c r="H4" s="5">
-        <v>43</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>18</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8447348839547373</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5928516341624629</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.07572341115599</v>
-      </c>
-      <c r="E5" s="4">
-        <v>90.85299744897968</v>
-      </c>
-      <c r="F5" s="4">
-        <v>75.60297818791946</v>
-      </c>
-      <c r="G5" s="5">
-        <v>64</v>
-      </c>
-      <c r="H5" s="5">
-        <v>34</v>
-      </c>
-      <c r="I5" s="5">
-        <v>15</v>
-      </c>
-      <c r="J5" s="5">
-        <v>15</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>9</v>
-      </c>
-      <c r="M5" s="5">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.009932837593625</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9946840431082778</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.021458896335105</v>
-      </c>
-      <c r="E3" s="4">
-        <v>90.10150935374152</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.35647371364641</v>
-      </c>
-      <c r="G3" s="5">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5">
-        <v>46</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>16</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>12</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.568142363120584</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.2979412036548</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.583705563801124</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90.50116921768706</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.80945889261764</v>
-      </c>
-      <c r="G4" s="5">
-        <v>64</v>
-      </c>
-      <c r="H4" s="5">
-        <v>33</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>28</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>14</v>
-      </c>
-      <c r="M4" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.643066006422165</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.246522736488108</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.490933127208385</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.0055272108844</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.03499021252802</v>
-      </c>
-      <c r="G5" s="5">
-        <v>64</v>
-      </c>
-      <c r="H5" s="5">
-        <v>28</v>
-      </c>
-      <c r="I5" s="5">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5">
-        <v>26</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>15</v>
-      </c>
-      <c r="M5" s="5">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/AraComputational2022.xlsx
+++ b/public/downloads/AraComputational2022.xlsx
@@ -1557,16 +1557,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7130465726328102</v>
+        <v>0.5244393935064409</v>
       </c>
       <c r="O3" s="5">
         <v>53</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5668498010017486</v>
+        <v>0.5196202885157029</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4914868155991595</v>
+        <v>0.4551205516693765</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -1616,22 +1616,22 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>0.8927313676963633</v>
+        <v>0.4734350914854524</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>0.796026340214369</v>
+        <v>0.7069023731788877</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6048734366198549</v>
+        <v>0.4787574853388047</v>
       </c>
       <c r="R4" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -1675,22 +1675,22 @@
         <v>9</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8468864625034654</v>
+        <v>0.5330450249557277</v>
       </c>
       <c r="O5" s="5">
         <v>52</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9680729191760813</v>
+        <v>0.9008960197655148</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7673180748055789</v>
+        <v>0.5864511299952045</v>
       </c>
       <c r="R5" s="5">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1857,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>1.061029127043414</v>
+        <v>1.043656416399415</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4886453862085142</v>
+        <v>0.4849718121149579</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4441892666045186</v>
+        <v>0.4429104825306101</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -1916,22 +1916,22 @@
         <v>9</v>
       </c>
       <c r="N4" s="4">
-        <v>1.696383812906371</v>
+        <v>1.446343040666989</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>1.282028587060316</v>
+        <v>1.187714478684136</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6078166474813875</v>
+        <v>0.515429977581226</v>
       </c>
       <c r="R4" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -1975,16 +1975,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>1.678105544845076</v>
+        <v>1.664226153412358</v>
       </c>
       <c r="O5" s="5">
         <v>47</v>
       </c>
       <c r="P5" s="4">
-        <v>0.770678926066161</v>
+        <v>0.7680765401725264</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5455872021909621</v>
+        <v>0.5449563207622021</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -2157,16 +2157,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1790374909568283</v>
+        <v>-0.233712488233726</v>
       </c>
       <c r="O3" s="5">
         <v>55</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3529583569173227</v>
+        <v>0.3442109689477191</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2505888739279591</v>
+        <v>0.2442715990956067</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -2216,16 +2216,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3235413195161727</v>
+        <v>-0.3529683997041957</v>
       </c>
       <c r="O4" s="5">
         <v>54</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5523744423840238</v>
+        <v>0.5478284675982066</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.32230351072836</v>
+        <v>0.3207006272382442</v>
       </c>
       <c r="R4" s="5">
         <v>53</v>
@@ -2275,16 +2275,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2132845692141044</v>
+        <v>-0.3936046071969326</v>
       </c>
       <c r="O5" s="5">
         <v>60</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5161011729185602</v>
+        <v>0.4987700346083367</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4358343744847943</v>
+        <v>0.4139782238095888</v>
       </c>
       <c r="R5" s="5">
         <v>59</v>
@@ -2457,22 +2457,22 @@
         <v>8</v>
       </c>
       <c r="N3" s="4">
-        <v>0.8800386901990487</v>
+        <v>0.5035670776944698</v>
       </c>
       <c r="O3" s="5">
         <v>47</v>
       </c>
       <c r="P3" s="4">
-        <v>0.919975553390493</v>
+        <v>0.8416811775063646</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5547109532503978</v>
+        <v>0.2690538495882369</v>
       </c>
       <c r="R3" s="5">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2516,22 +2516,22 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>1.194751372003503</v>
+        <v>0.6308391971729179</v>
       </c>
       <c r="O4" s="5">
         <v>51</v>
       </c>
       <c r="P4" s="4">
-        <v>1.084181267634807</v>
+        <v>0.960749281625769</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8622284025363476</v>
+        <v>0.4882669447350724</v>
       </c>
       <c r="R4" s="5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S4" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2575,22 +2575,22 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>1.162286996974362</v>
+        <v>0.6111840540848057</v>
       </c>
       <c r="O5" s="5">
         <v>52</v>
       </c>
       <c r="P5" s="4">
-        <v>1.148377284845395</v>
+        <v>1.032118688967811</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8034795681356607</v>
+        <v>0.43812410841541</v>
       </c>
       <c r="R5" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2757,16 +2757,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2782070042260623</v>
+        <v>0.1450738869356201</v>
       </c>
       <c r="O3" s="5">
         <v>54</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4989382052298792</v>
+        <v>0.4775173524554048</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.432562834828403</v>
+        <v>0.4092080902948951</v>
       </c>
       <c r="R3" s="5">
         <v>53</v>
@@ -2816,22 +2816,22 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6136638985816594</v>
+        <v>0.07933947041919964</v>
       </c>
       <c r="O4" s="5">
         <v>56</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9050294696833273</v>
+        <v>0.8243132963650892</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7687924275991252</v>
+        <v>0.4050033933550474</v>
       </c>
       <c r="R4" s="5">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="S4" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2875,16 +2875,16 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5369695497644357</v>
+        <v>0.1487092455593437</v>
       </c>
       <c r="O5" s="5">
         <v>59</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8167869444095512</v>
+        <v>0.7632407919187223</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6132195809269937</v>
+        <v>0.4922374292037754</v>
       </c>
       <c r="R5" s="5">
         <v>54</v>
@@ -3057,16 +3057,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7840541456704667</v>
+        <v>0.5042831093668951</v>
       </c>
       <c r="O3" s="5">
         <v>50</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6930207737133075</v>
+        <v>0.6293633504609462</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5949409141917382</v>
+        <v>0.5057574450869887</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -3116,22 +3116,22 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>1.187756106315856</v>
+        <v>0.6333278378393743</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>1.023942865462487</v>
+        <v>0.9537401106361986</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7559524592722544</v>
+        <v>0.4436996907477119</v>
       </c>
       <c r="R4" s="5">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3175,22 +3175,22 @@
         <v>11</v>
       </c>
       <c r="N5" s="4">
-        <v>1.247213572259313</v>
+        <v>0.8791266314885666</v>
       </c>
       <c r="O5" s="5">
         <v>48</v>
       </c>
       <c r="P5" s="4">
-        <v>1.005984222359067</v>
+        <v>0.9277578705644983</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7036440639182364</v>
+        <v>0.4968648455091293</v>
       </c>
       <c r="R5" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3357,13 +3357,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08963091676242503</v>
+        <v>-0.08608303803890749</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2171080173445042</v>
+        <v>0.2172188885546141</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1633704386971049</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1881153155310177</v>
+        <v>-0.1394885738367861</v>
       </c>
       <c r="O4" s="5">
         <v>51</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4581759911648445</v>
+        <v>0.4634670357379237</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2481861045267076</v>
+        <v>0.2443377259784826</v>
       </c>
       <c r="R4" s="5">
         <v>51</v>
@@ -3475,16 +3475,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2516221627271897</v>
+        <v>-0.2501472835685119</v>
       </c>
       <c r="O5" s="5">
         <v>60</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3432093397403266</v>
+        <v>0.3431171597929092</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3114191807300002</v>
+        <v>0.3114441786818423</v>
       </c>
       <c r="R5" s="5">
         <v>59</v>
@@ -3657,16 +3657,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1687291093951412</v>
+        <v>-0.2795074985323538</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3361167581606996</v>
+        <v>0.3188606690946094</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2124096892155558</v>
+        <v>0.183317028760892</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -3716,22 +3716,22 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01604855497318088</v>
+        <v>-0.4606761761415754</v>
       </c>
       <c r="O4" s="5">
         <v>52</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8178605971398287</v>
+        <v>0.6804810789811166</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5579218232855837</v>
+        <v>0.1836510485704663</v>
       </c>
       <c r="R4" s="5">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S4" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3775,22 +3775,22 @@
         <v>6</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1827495203971199</v>
+        <v>-0.1235277515402515</v>
       </c>
       <c r="O5" s="5">
         <v>60</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6384068399364047</v>
+        <v>0.5366108442776549</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3984337813526177</v>
+        <v>0.2157270504094445</v>
       </c>
       <c r="R5" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3957,16 +3957,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02145925383666704</v>
+        <v>0.0150532458007433</v>
       </c>
       <c r="O3" s="5">
         <v>55</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2351552217061387</v>
+        <v>0.235145658581996</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1685872175421188</v>
+        <v>0.1683386239121747</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.131296056778872</v>
+        <v>0.1172485146178328</v>
       </c>
       <c r="O4" s="5">
         <v>46</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4309949533725967</v>
+        <v>0.4295035938995607</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2294618663124265</v>
+        <v>0.2288457424318726</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -4075,16 +4075,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05913518391144909</v>
+        <v>-0.01551054516352224</v>
       </c>
       <c r="O5" s="5">
         <v>57</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3290099045310935</v>
+        <v>0.3190342386541241</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2736832335635749</v>
+        <v>0.2668854585767843</v>
       </c>
       <c r="R5" s="5">
         <v>56</v>
@@ -4257,22 +4257,22 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2613181096570754</v>
+        <v>-0.2015021569068001</v>
       </c>
       <c r="O3" s="5">
         <v>53</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8551231335009826</v>
+        <v>0.7232013965929405</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6468840139789233</v>
+        <v>0.1768462753935392</v>
       </c>
       <c r="R3" s="5">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="S3" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4316,22 +4316,22 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2652448560984837</v>
+        <v>-0.2727248144890382</v>
       </c>
       <c r="O4" s="5">
         <v>51</v>
       </c>
       <c r="P4" s="4">
-        <v>1.028471441325691</v>
+        <v>0.9478085409730852</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6718907647985274</v>
+        <v>0.1890555482173704</v>
       </c>
       <c r="R4" s="5">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="S4" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -4375,22 +4375,22 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2873073210433201</v>
+        <v>-0.1389827296928328</v>
       </c>
       <c r="O5" s="5">
         <v>52</v>
       </c>
       <c r="P5" s="4">
-        <v>1.026065459920642</v>
+        <v>0.9380171405997252</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5950428411525783</v>
+        <v>0.2519128596427166</v>
       </c>
       <c r="R5" s="5">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S5" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4503,13 +4503,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>48.4375</v>
+        <v>48.95833333333333</v>
       </c>
       <c r="C3" s="3">
         <v>6.770833333333333</v>
       </c>
       <c r="D3" s="3">
-        <v>44.79166666666667</v>
+        <v>44.27083333333333</v>
       </c>
       <c r="E3" s="3">
         <v>1.041666666666667</v>
@@ -4518,16 +4518,16 @@
         <v>39.58333333333333</v>
       </c>
       <c r="G3" s="3">
-        <v>4.166666666666666</v>
+        <v>3.645833333333333</v>
       </c>
       <c r="H3" s="4">
-        <v>1.003233611525728</v>
+        <v>1.018895197887828</v>
       </c>
       <c r="I3" s="4">
-        <v>0.6290038801359723</v>
+        <v>0.6285764779471616</v>
       </c>
       <c r="J3" s="4">
-        <v>0.8898350282420524</v>
+        <v>0.8977132276585964</v>
       </c>
       <c r="K3" s="4">
         <v>87.38679846938778</v>
@@ -4571,13 +4571,13 @@
         <v>4.6875</v>
       </c>
       <c r="H4" s="4">
-        <v>0.7817919373302517</v>
+        <v>0.7714616221120917</v>
       </c>
       <c r="I4" s="4">
-        <v>0.563787646102885</v>
+        <v>0.552125588106011</v>
       </c>
       <c r="J4" s="4">
-        <v>0.6065695373071569</v>
+        <v>0.5962621934618341</v>
       </c>
       <c r="K4" s="4">
         <v>89.72027352607695</v>
@@ -4603,13 +4603,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>76.5625</v>
+        <v>69.79166666666666</v>
       </c>
       <c r="C5" s="3">
         <v>4.6875</v>
       </c>
       <c r="D5" s="3">
-        <v>18.75</v>
+        <v>25.52083333333333</v>
       </c>
       <c r="E5" s="3">
         <v>1.041666666666667</v>
@@ -4618,16 +4618,16 @@
         <v>10.41666666666667</v>
       </c>
       <c r="G5" s="3">
-        <v>7.291666666666667</v>
+        <v>14.0625</v>
       </c>
       <c r="H5" s="4">
-        <v>1.025044931378842</v>
+        <v>0.9478502646386834</v>
       </c>
       <c r="I5" s="4">
-        <v>0.7923443318874139</v>
+        <v>0.4544534803541482</v>
       </c>
       <c r="J5" s="4">
-        <v>1.066350117528539</v>
+        <v>0.9925682135472814</v>
       </c>
       <c r="K5" s="4">
         <v>95.84449404761904</v>
@@ -4671,13 +4671,13 @@
         <v>2.083333333333333</v>
       </c>
       <c r="H6" s="4">
-        <v>0.7366094342142514</v>
+        <v>0.7254191765829709</v>
       </c>
       <c r="I6" s="4">
-        <v>0.43648936203786</v>
+        <v>0.431231474246924</v>
       </c>
       <c r="J6" s="4">
-        <v>0.5504762921307507</v>
+        <v>0.5435593543265186</v>
       </c>
       <c r="K6" s="4">
         <v>91.00340136054443</v>
@@ -4703,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>81.77083333333334</v>
+        <v>73.4375</v>
       </c>
       <c r="C7" s="3">
         <v>2.604166666666667</v>
       </c>
       <c r="D7" s="3">
-        <v>15.625</v>
+        <v>23.95833333333334</v>
       </c>
       <c r="E7" s="3">
         <v>1.041666666666667</v>
@@ -4718,16 +4718,16 @@
         <v>7.291666666666667</v>
       </c>
       <c r="G7" s="3">
-        <v>7.291666666666667</v>
+        <v>15.625</v>
       </c>
       <c r="H7" s="4">
-        <v>0.9702441939570171</v>
+        <v>0.8226821191859713</v>
       </c>
       <c r="I7" s="4">
-        <v>0.7595440448405081</v>
+        <v>0.3166994921244953</v>
       </c>
       <c r="J7" s="4">
-        <v>1.000430152114304</v>
+        <v>0.8686818577748904</v>
       </c>
       <c r="K7" s="4">
         <v>97.2006094104308</v>
@@ -4753,13 +4753,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>71.875</v>
+        <v>69.79166666666666</v>
       </c>
       <c r="C8" s="3">
         <v>10.41666666666667</v>
       </c>
       <c r="D8" s="3">
-        <v>17.70833333333334</v>
+        <v>19.79166666666666</v>
       </c>
       <c r="E8" s="3">
         <v>0.5208333333333333</v>
@@ -4768,16 +4768,16 @@
         <v>14.0625</v>
       </c>
       <c r="G8" s="3">
-        <v>3.125</v>
+        <v>5.208333333333334</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7769830201307331</v>
+        <v>0.7091395604867019</v>
       </c>
       <c r="I8" s="4">
-        <v>0.6198276610982919</v>
+        <v>0.5065544040207758</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8277863007810878</v>
+        <v>0.790359449810753</v>
       </c>
       <c r="K8" s="4">
         <v>92.90072278911578</v>
@@ -4803,13 +4803,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>66.14583333333334</v>
+        <v>65.625</v>
       </c>
       <c r="C9" s="3">
         <v>7.8125</v>
       </c>
       <c r="D9" s="3">
-        <v>26.04166666666667</v>
+        <v>26.5625</v>
       </c>
       <c r="E9" s="3">
         <v>1.5625</v>
@@ -4818,16 +4818,16 @@
         <v>21.35416666666666</v>
       </c>
       <c r="G9" s="3">
-        <v>3.125</v>
+        <v>3.645833333333333</v>
       </c>
       <c r="H9" s="4">
-        <v>0.8471176331116638</v>
+        <v>0.8135876103238733</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5244134201202187</v>
+        <v>0.4981142897838718</v>
       </c>
       <c r="J9" s="4">
-        <v>0.6390875361240212</v>
+        <v>0.6132327469657747</v>
       </c>
       <c r="K9" s="4">
         <v>88.86940192743762</v>
@@ -4871,13 +4871,13 @@
         <v>1.5625</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4738113240733022</v>
+        <v>0.4636031570514209</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3393259840681671</v>
+        <v>0.3289910530093701</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4034397655824717</v>
+        <v>0.3958125810014133</v>
       </c>
       <c r="K10" s="4">
         <v>95.23667800453514</v>
@@ -4903,13 +4903,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>68.22916666666666</v>
+        <v>64.0625</v>
       </c>
       <c r="C11" s="3">
         <v>4.6875</v>
       </c>
       <c r="D11" s="3">
-        <v>27.08333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="E11" s="3">
         <v>0.5208333333333333</v>
@@ -4918,16 +4918,16 @@
         <v>16.66666666666666</v>
       </c>
       <c r="G11" s="3">
-        <v>9.895833333333332</v>
+        <v>14.0625</v>
       </c>
       <c r="H11" s="4">
-        <v>1.050844701956898</v>
+        <v>0.9448497160333149</v>
       </c>
       <c r="I11" s="4">
-        <v>0.7462500503657051</v>
+        <v>0.4016384094818009</v>
       </c>
       <c r="J11" s="4">
-        <v>1.092960240325064</v>
+        <v>0.9888831686225386</v>
       </c>
       <c r="K11" s="4">
         <v>94.15302579365077</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>82.29166666666666</v>
+        <v>79.6875</v>
       </c>
       <c r="C12" s="3">
         <v>5.208333333333334</v>
       </c>
       <c r="D12" s="3">
-        <v>12.5</v>
+        <v>15.10416666666667</v>
       </c>
       <c r="E12" s="3">
         <v>1.041666666666667</v>
@@ -4968,16 +4968,16 @@
         <v>5.729166666666666</v>
       </c>
       <c r="G12" s="3">
-        <v>5.729166666666666</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="H12" s="4">
-        <v>0.7402515397742526</v>
+        <v>0.6883571469130721</v>
       </c>
       <c r="I12" s="4">
-        <v>0.6028360849589771</v>
+        <v>0.4372484056010815</v>
       </c>
       <c r="J12" s="4">
-        <v>0.7923833969233</v>
+        <v>0.743313462130855</v>
       </c>
       <c r="K12" s="4">
         <v>96.65904903628119</v>
@@ -5003,13 +5003,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>70.3125</v>
+        <v>67.1875</v>
       </c>
       <c r="C13" s="3">
         <v>9.375</v>
       </c>
       <c r="D13" s="3">
-        <v>20.3125</v>
+        <v>23.4375</v>
       </c>
       <c r="E13" s="3">
         <v>3.125</v>
@@ -5018,16 +5018,16 @@
         <v>13.02083333333333</v>
       </c>
       <c r="G13" s="3">
-        <v>4.166666666666666</v>
+        <v>7.291666666666667</v>
       </c>
       <c r="H13" s="4">
-        <v>0.9076492871782872</v>
+        <v>0.8369537772205478</v>
       </c>
       <c r="I13" s="4">
-        <v>0.6816552477208353</v>
+        <v>0.4841005334474391</v>
       </c>
       <c r="J13" s="4">
-        <v>0.9860543141725202</v>
+        <v>0.9407356142695402</v>
       </c>
       <c r="K13" s="4">
         <v>93.54237528344734</v>
@@ -5071,13 +5071,13 @@
         <v>1.041666666666667</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3394977827498918</v>
+        <v>0.341267694695149</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2420479973552408</v>
+        <v>0.2408745490010192</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2907678317909027</v>
+        <v>0.2904168651766737</v>
       </c>
       <c r="K14" s="4">
         <v>96.12174036281176</v>
@@ -5103,13 +5103,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>83.33333333333334</v>
+        <v>81.25</v>
       </c>
       <c r="C15" s="3">
         <v>4.166666666666666</v>
       </c>
       <c r="D15" s="3">
-        <v>12.5</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="E15" s="3">
         <v>1.041666666666667</v>
@@ -5118,16 +5118,16 @@
         <v>6.25</v>
       </c>
       <c r="G15" s="3">
-        <v>5.208333333333334</v>
+        <v>7.291666666666667</v>
       </c>
       <c r="H15" s="4">
-        <v>0.5974613984123111</v>
+        <v>0.5119841974511269</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3800091111086792</v>
+        <v>0.1946322342766143</v>
       </c>
       <c r="J15" s="4">
-        <v>0.6412784606711187</v>
+        <v>0.5659062191015699</v>
       </c>
       <c r="K15" s="4">
         <v>96.9357638888893</v>
@@ -5171,13 +5171,13 @@
         <v>1.041666666666667</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3317200265366096</v>
+        <v>0.3278944970452269</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2242642094692707</v>
+        <v>0.2215562533552788</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2514901336086094</v>
+        <v>0.2490399071215905</v>
       </c>
       <c r="K16" s="4">
         <v>94.46517148526091</v>
@@ -5203,13 +5203,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>74.47916666666666</v>
+        <v>68.22916666666666</v>
       </c>
       <c r="C17" s="3">
         <v>6.770833333333333</v>
       </c>
       <c r="D17" s="3">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
         <v>2.083333333333333</v>
@@ -5218,16 +5218,16 @@
         <v>9.895833333333332</v>
       </c>
       <c r="G17" s="3">
-        <v>6.770833333333333</v>
+        <v>13.02083333333333</v>
       </c>
       <c r="H17" s="4">
-        <v>0.969886678249105</v>
+        <v>0.869675692721917</v>
       </c>
       <c r="I17" s="4">
-        <v>0.6380643088438406</v>
+        <v>0.2065469299722712</v>
       </c>
       <c r="J17" s="4">
-        <v>1.085070782117644</v>
+        <v>1.004271610380488</v>
       </c>
       <c r="K17" s="4">
         <v>96.39508928571465</v>
@@ -6110,13 +6110,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="5">
         <v>13</v>
       </c>
       <c r="D3" s="5">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" s="5">
         <v>2</v>
@@ -6125,7 +6125,7 @@
         <v>76</v>
       </c>
       <c r="G3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" s="5">
         <v>2</v>
@@ -6198,13 +6198,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C5" s="5">
         <v>9</v>
       </c>
       <c r="D5" s="5">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E5" s="5">
         <v>2</v>
@@ -6213,7 +6213,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="5">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H5" s="5">
         <v>2</v>
@@ -6286,13 +6286,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C7" s="5">
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -6301,7 +6301,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="5">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5">
         <v>2</v>
@@ -6330,13 +6330,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C8" s="5">
         <v>20</v>
       </c>
       <c r="D8" s="5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -6345,7 +6345,7 @@
         <v>27</v>
       </c>
       <c r="G8" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -6374,13 +6374,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C9" s="5">
         <v>15</v>
       </c>
       <c r="D9" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -6389,7 +6389,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="5">
         <v>3</v>
@@ -6462,13 +6462,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5">
         <v>9</v>
       </c>
       <c r="D11" s="5">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -6477,7 +6477,7 @@
         <v>32</v>
       </c>
       <c r="G11" s="5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5">
         <v>1</v>
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C12" s="5">
         <v>10</v>
       </c>
       <c r="D12" s="5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5">
         <v>2</v>
@@ -6521,7 +6521,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5">
         <v>2</v>
@@ -6550,13 +6550,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C13" s="5">
         <v>18</v>
       </c>
       <c r="D13" s="5">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E13" s="5">
         <v>6</v>
@@ -6565,7 +6565,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H13" s="5">
         <v>6</v>
@@ -6638,13 +6638,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C15" s="5">
         <v>8</v>
       </c>
       <c r="D15" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E15" s="5">
         <v>2</v>
@@ -6653,7 +6653,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H15" s="5">
         <v>2</v>
@@ -6726,13 +6726,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C17" s="5">
         <v>13</v>
       </c>
       <c r="D17" s="5">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E17" s="5">
         <v>4</v>
@@ -6741,7 +6741,7 @@
         <v>19</v>
       </c>
       <c r="G17" s="5">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H17" s="5">
         <v>4</v>
@@ -6924,16 +6924,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7795812446487741</v>
+        <v>0.6170387387651317</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7868286216861956</v>
+        <v>0.8155544268790017</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3922330359307251</v>
+        <v>0.3624017111667789</v>
       </c>
       <c r="R3" s="5">
         <v>31</v>
@@ -6983,16 +6983,16 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>1.538513566617478</v>
+        <v>1.428508334194333</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>1.048511152901003</v>
+        <v>1.043292609168683</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6665757316990029</v>
+        <v>0.6538902450906711</v>
       </c>
       <c r="R4" s="5">
         <v>35</v>
@@ -7042,22 +7042,22 @@
         <v>17</v>
       </c>
       <c r="N5" s="4">
-        <v>1.985547438153483</v>
+        <v>2.064368473281149</v>
       </c>
       <c r="O5" s="5">
         <v>31</v>
       </c>
       <c r="P5" s="4">
-        <v>1.174361059989987</v>
+        <v>1.1978385576158</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8521476344195503</v>
+        <v>0.8916277608103412</v>
       </c>
       <c r="R5" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7224,16 +7224,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9748091222858898</v>
+        <v>0.9102988528515539</v>
       </c>
       <c r="O3" s="5">
         <v>50</v>
       </c>
       <c r="P3" s="4">
-        <v>0.650361487585953</v>
+        <v>0.6476854915483088</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5708269785345039</v>
+        <v>0.5686483361472611</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -7283,22 +7283,22 @@
         <v>20</v>
       </c>
       <c r="N4" s="4">
-        <v>2.049461377170462</v>
+        <v>1.943928027343702</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9127790199725443</v>
+        <v>0.8904622408075573</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4629920204068526</v>
+        <v>0.4827662783742596</v>
       </c>
       <c r="R4" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7342,22 +7342,22 @@
         <v>16</v>
       </c>
       <c r="N5" s="4">
-        <v>1.655141997710326</v>
+        <v>1.543937265039034</v>
       </c>
       <c r="O5" s="5">
         <v>46</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7822353044322575</v>
+        <v>0.7762371339804091</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6491710297456453</v>
+        <v>0.6000465084779328</v>
       </c>
       <c r="R5" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7524,22 +7524,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.398000250551454</v>
+        <v>0.0866033898743801</v>
       </c>
       <c r="O3" s="5">
         <v>53</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7577917781775221</v>
+        <v>0.724851726467954</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5422904777537053</v>
+        <v>0.4061601164453942</v>
       </c>
       <c r="R3" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7583,22 +7583,22 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7838972193724164</v>
+        <v>0.08137054898634233</v>
       </c>
       <c r="O4" s="5">
         <v>51</v>
       </c>
       <c r="P4" s="4">
-        <v>1.130290796946263</v>
+        <v>0.9950231519911252</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.9406114630275214</v>
+        <v>0.4004577860973937</v>
       </c>
       <c r="R4" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="S4" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7642,22 +7642,22 @@
         <v>15</v>
       </c>
       <c r="N5" s="4">
-        <v>1.183966738448005</v>
+        <v>0.6898732184350926</v>
       </c>
       <c r="O5" s="5">
         <v>57</v>
       </c>
       <c r="P5" s="4">
-        <v>1.187052219012742</v>
+        <v>1.123675915456971</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.902260054580481</v>
+        <v>0.5550357603941285</v>
       </c>
       <c r="R5" s="5">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="S5" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -7824,16 +7824,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5958395602820948</v>
+        <v>0.5609273377082875</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3911462275278442</v>
+        <v>0.3864502301778595</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3420507307755912</v>
+        <v>0.339165117985199</v>
       </c>
       <c r="R3" s="5">
         <v>51</v>
@@ -7883,16 +7883,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>1.098444606099456</v>
+        <v>1.04506159600747</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>1.12436299610429</v>
+        <v>1.109402014974213</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4892464162241351</v>
+        <v>0.4813237494436081</v>
       </c>
       <c r="R4" s="5">
         <v>40</v>
@@ -7942,16 +7942,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9578985741430226</v>
+        <v>0.8799349037589117</v>
       </c>
       <c r="O5" s="5">
         <v>49</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6943190790106201</v>
+        <v>0.6804052845968402</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4928661959321246</v>
+        <v>0.4873084151111033</v>
       </c>
       <c r="R5" s="5">
         <v>48</v>
@@ -8124,22 +8124,22 @@
         <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5874900262169779</v>
+        <v>0.1643719583541383</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8448886680353618</v>
+        <v>0.7162571257488769</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6956149133391002</v>
+        <v>0.2400396645552648</v>
       </c>
       <c r="R3" s="5">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -8183,22 +8183,22 @@
         <v>13</v>
       </c>
       <c r="N4" s="4">
-        <v>0.8581304658900576</v>
+        <v>0.2520421840823701</v>
       </c>
       <c r="O4" s="5">
         <v>59</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9597961092371899</v>
+        <v>0.784825197816479</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8107434010541894</v>
+        <v>0.3222529168507922</v>
       </c>
       <c r="R4" s="5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="S4" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -8242,22 +8242,22 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8818604746063728</v>
+        <v>0.3520209861963508</v>
       </c>
       <c r="O5" s="5">
         <v>55</v>
       </c>
       <c r="P5" s="4">
-        <v>1.1060478045985</v>
+        <v>0.9669640339925583</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7727983887847495</v>
+        <v>0.3892309597090948</v>
       </c>
       <c r="R5" s="5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S5" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
